--- a/research/traditional_assets/database/data/finland/finland_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_semiconductor.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.289</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
-        <v>-0.5241935483870969</v>
+        <v>0.09459459459459438</v>
       </c>
       <c r="H2">
-        <v>-1.600806451612903</v>
+        <v>-2.290540540540541</v>
       </c>
       <c r="I2">
-        <v>-1.653225806451613</v>
+        <v>-2.921593554193716</v>
       </c>
       <c r="J2">
-        <v>-1.653225806451613</v>
+        <v>-2.921593554193716</v>
       </c>
       <c r="K2">
-        <v>-6.01</v>
+        <v>-6.21</v>
       </c>
       <c r="L2">
-        <v>-2.423387096774194</v>
+        <v>-4.195945945945946</v>
       </c>
       <c r="M2">
-        <v>0.068</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002029850746268657</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.01131447587354409</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +627,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.068</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="V2">
-        <v>0.0009850746268656716</v>
+        <v>0.0007936507936507937</v>
       </c>
       <c r="W2">
-        <v>4.202797202797202</v>
+        <v>4.669172932330826</v>
       </c>
       <c r="X2">
-        <v>0.1100439786109605</v>
+        <v>0.2735994706992634</v>
       </c>
       <c r="Y2">
-        <v>4.092753224186242</v>
+        <v>4.395573461631563</v>
       </c>
       <c r="Z2">
-        <v>0.1904030710172745</v>
+        <v>0.1005858972126475</v>
       </c>
       <c r="AA2">
-        <v>-0.3147792706333973</v>
+        <v>-0.2938711089392627</v>
       </c>
       <c r="AB2">
-        <v>0.08211769375988998</v>
+        <v>0.1435384543405164</v>
       </c>
       <c r="AC2">
-        <v>-0.3968969643932873</v>
+        <v>-0.4374095632797791</v>
       </c>
       <c r="AD2">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.1997923010335008</v>
       </c>
       <c r="AF2">
-        <v>16.4</v>
+        <v>17.6997923010335</v>
       </c>
       <c r="AG2">
-        <v>16.367</v>
+        <v>17.6897923010335</v>
       </c>
       <c r="AH2">
-        <v>0.3286573146292585</v>
+        <v>0.5841555653313761</v>
       </c>
       <c r="AI2">
-        <v>1.088254810882548</v>
+        <v>1.279830666705732</v>
       </c>
       <c r="AJ2">
-        <v>0.3282130467042332</v>
+        <v>0.5840182766928355</v>
       </c>
       <c r="AK2">
-        <v>1.088448493715502</v>
+        <v>1.280033152141555</v>
       </c>
       <c r="AL2">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AM2">
-        <v>1.429</v>
+        <v>1.56</v>
       </c>
       <c r="AN2">
-        <v>-4.293193717277487</v>
+        <v>-4.338125929598414</v>
       </c>
       <c r="AO2">
-        <v>-2.867132867132867</v>
+        <v>-2.814102564102564</v>
       </c>
       <c r="AP2">
-        <v>-4.284554973821989</v>
+        <v>-4.385174095447075</v>
       </c>
       <c r="AQ2">
-        <v>-2.869139258222533</v>
+        <v>-2.814102564102564</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +716,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.289</v>
+        <v>0.215</v>
       </c>
       <c r="G3">
-        <v>-0.5241935483870969</v>
+        <v>0.09459459459459438</v>
       </c>
       <c r="H3">
-        <v>-1.600806451612903</v>
+        <v>-2.290540540540541</v>
       </c>
       <c r="I3">
-        <v>-1.653225806451613</v>
+        <v>-2.921593554193716</v>
       </c>
       <c r="J3">
-        <v>-1.653225806451613</v>
+        <v>-2.921593554193716</v>
       </c>
       <c r="K3">
-        <v>-6.01</v>
+        <v>-6.21</v>
       </c>
       <c r="L3">
-        <v>-2.423387096774194</v>
+        <v>-4.195945945945946</v>
       </c>
       <c r="M3">
-        <v>0.068</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.002029850746268657</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.01131447587354409</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +755,76 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.068</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="V3">
-        <v>0.0009850746268656716</v>
+        <v>0.0007936507936507937</v>
       </c>
       <c r="W3">
-        <v>4.202797202797202</v>
+        <v>4.669172932330826</v>
       </c>
       <c r="X3">
-        <v>0.1100439786109605</v>
+        <v>0.2735994706992634</v>
       </c>
       <c r="Y3">
-        <v>4.092753224186242</v>
+        <v>4.395573461631563</v>
       </c>
       <c r="Z3">
-        <v>0.1904030710172745</v>
+        <v>0.1005858972126475</v>
       </c>
       <c r="AA3">
-        <v>-0.3147792706333973</v>
+        <v>-0.2938711089392627</v>
       </c>
       <c r="AB3">
-        <v>0.08211769375988998</v>
+        <v>0.1435384543405164</v>
       </c>
       <c r="AC3">
-        <v>-0.3968969643932873</v>
+        <v>-0.4374095632797791</v>
       </c>
       <c r="AD3">
-        <v>16.4</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.1997923010335008</v>
       </c>
       <c r="AF3">
-        <v>16.4</v>
+        <v>17.6997923010335</v>
       </c>
       <c r="AG3">
-        <v>16.367</v>
+        <v>17.6897923010335</v>
       </c>
       <c r="AH3">
-        <v>0.3286573146292585</v>
+        <v>0.5841555653313761</v>
       </c>
       <c r="AI3">
-        <v>1.088254810882548</v>
+        <v>1.279830666705732</v>
       </c>
       <c r="AJ3">
-        <v>0.3282130467042332</v>
+        <v>0.5840182766928355</v>
       </c>
       <c r="AK3">
-        <v>1.088448493715502</v>
+        <v>1.280033152141555</v>
       </c>
       <c r="AL3">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AM3">
-        <v>1.429</v>
+        <v>1.56</v>
       </c>
       <c r="AN3">
-        <v>-4.293193717277487</v>
+        <v>-4.338125929598414</v>
       </c>
       <c r="AO3">
-        <v>-2.867132867132867</v>
+        <v>-2.814102564102564</v>
       </c>
       <c r="AP3">
-        <v>-4.284554973821989</v>
+        <v>-4.385174095447075</v>
       </c>
       <c r="AQ3">
-        <v>-2.869139258222533</v>
+        <v>-2.814102564102564</v>
       </c>
     </row>
   </sheetData>
